--- a/research/traditional_assets/database/data/argentina/argentina_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_precious_metals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.112</v>
+        <v>-0.118</v>
       </c>
       <c r="G2">
-        <v>0.08579545454545454</v>
+        <v>-0.2711267605633803</v>
       </c>
       <c r="H2">
-        <v>0.08579545454545454</v>
+        <v>-0.2711267605633803</v>
       </c>
       <c r="I2">
-        <v>-0.3863636363636363</v>
+        <v>-1.190140845070423</v>
       </c>
       <c r="J2">
-        <v>-0.3863636363636363</v>
+        <v>-1.190140845070423</v>
       </c>
       <c r="K2">
-        <v>-8.32</v>
+        <v>-12.1</v>
       </c>
       <c r="L2">
-        <v>-0.4727272727272727</v>
+        <v>-0.852112676056338</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.003868471953578337</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.001652892561983471</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,64 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>5.151999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="V2">
-        <v>0.09739130434782606</v>
+        <v>0.08549323017408124</v>
+      </c>
+      <c r="W2">
+        <v>-0.4708171206225681</v>
       </c>
       <c r="X2">
-        <v>0.2374847585830585</v>
+        <v>1.418785559773485</v>
+      </c>
+      <c r="Y2">
+        <v>-1.889602680396053</v>
       </c>
       <c r="Z2">
-        <v>0.4698721200309689</v>
+        <v>0.3438423168192164</v>
+      </c>
+      <c r="AA2">
+        <v>-0.4092207855101941</v>
       </c>
       <c r="AB2">
-        <v>0.1851058101391622</v>
+        <v>0.3787528471016532</v>
+      </c>
+      <c r="AC2">
+        <v>-0.7879736326118474</v>
       </c>
       <c r="AD2">
-        <v>20.393</v>
+        <v>29.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>20.393</v>
+        <v>29.4</v>
       </c>
       <c r="AG2">
-        <v>15.241</v>
+        <v>28.958</v>
       </c>
       <c r="AH2">
-        <v>0.2782393953037807</v>
+        <v>0.8504483656349435</v>
       </c>
       <c r="AI2">
-        <v>0.4179492960055746</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="AJ2">
-        <v>0.2236685695836574</v>
+        <v>0.8485114861697139</v>
       </c>
       <c r="AK2">
-        <v>0.3492358103618158</v>
+        <v>0.733894267322216</v>
       </c>
       <c r="AL2">
-        <v>1.101</v>
+        <v>2.9</v>
       </c>
       <c r="AM2">
-        <v>0.877</v>
+        <v>2.708</v>
       </c>
       <c r="AN2">
-        <v>-8.497083333333334</v>
+        <v>-2.556521739130435</v>
       </c>
       <c r="AO2">
-        <v>-6.176203451407811</v>
+        <v>-5.827586206896552</v>
       </c>
       <c r="AP2">
-        <v>-6.350416666666668</v>
+        <v>-2.518086956521739</v>
       </c>
       <c r="AQ2">
-        <v>-7.753705815279361</v>
+        <v>-6.240768094534712</v>
       </c>
     </row>
     <row r="3">
@@ -704,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.112</v>
+        <v>-0.118</v>
       </c>
       <c r="G3">
-        <v>0.08579545454545454</v>
+        <v>-0.2711267605633803</v>
       </c>
       <c r="H3">
-        <v>0.08579545454545454</v>
+        <v>-0.2711267605633803</v>
       </c>
       <c r="I3">
-        <v>-0.3079545454545454</v>
+        <v>-1.190140845070423</v>
       </c>
       <c r="J3">
-        <v>-0.3079545454545454</v>
+        <v>-1.190140845070423</v>
       </c>
       <c r="K3">
-        <v>-7.03</v>
+        <v>-12.1</v>
       </c>
       <c r="L3">
-        <v>-0.3994318181818182</v>
+        <v>-0.852112676056338</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.003868471953578337</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.001652892561983471</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -743,165 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.592</v>
+        <v>0.442</v>
       </c>
       <c r="V3">
-        <v>0.03252747252747253</v>
+        <v>0.08549323017408124</v>
       </c>
       <c r="W3">
-        <v>-0.5325757575757576</v>
+        <v>-0.4708171206225681</v>
       </c>
       <c r="X3">
-        <v>0.3024181375210049</v>
+        <v>1.418785559773485</v>
       </c>
       <c r="Y3">
-        <v>-0.8349938950967625</v>
+        <v>-1.889602680396053</v>
       </c>
       <c r="Z3">
-        <v>0.4698721200309689</v>
+        <v>0.3438423168192164</v>
       </c>
       <c r="AA3">
-        <v>-0.1446992551459006</v>
+        <v>-0.4092207855101941</v>
       </c>
       <c r="AB3">
-        <v>0.1980624909002862</v>
+        <v>0.3787528471016532</v>
       </c>
       <c r="AC3">
-        <v>-0.3427617460461869</v>
+        <v>-0.7879736326118474</v>
       </c>
       <c r="AD3">
-        <v>20.2</v>
+        <v>29.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>20.2</v>
+        <v>29.4</v>
       </c>
       <c r="AG3">
-        <v>19.608</v>
+        <v>28.958</v>
       </c>
       <c r="AH3">
-        <v>0.5260416666666666</v>
+        <v>0.8504483656349435</v>
       </c>
       <c r="AI3">
-        <v>0.4539325842696629</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="AJ3">
-        <v>0.5186203977994075</v>
+        <v>0.8485114861697139</v>
       </c>
       <c r="AK3">
-        <v>0.4465701011205248</v>
+        <v>0.733894267322216</v>
       </c>
       <c r="AL3">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="AM3">
-        <v>0.8760000000000001</v>
+        <v>2.708</v>
       </c>
       <c r="AN3">
-        <v>-8.416666666666666</v>
+        <v>-2.556521739130435</v>
       </c>
       <c r="AO3">
-        <v>-4.927272727272727</v>
+        <v>-5.827586206896552</v>
       </c>
       <c r="AP3">
-        <v>-8.17</v>
+        <v>-2.518086956521739</v>
       </c>
       <c r="AQ3">
-        <v>-6.187214611872145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Fredonia Mining Inc. (TSXV:FRED)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Precious Metals</t>
-        </is>
-      </c>
-      <c r="K4">
-        <v>-1.29</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>4.56</v>
-      </c>
-      <c r="V4">
-        <v>0.1314121037463977</v>
-      </c>
-      <c r="X4">
-        <v>0.172551379645112</v>
-      </c>
-      <c r="AB4">
-        <v>0.1721491293780382</v>
-      </c>
-      <c r="AD4">
-        <v>0.193</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0.193</v>
-      </c>
-      <c r="AG4">
-        <v>-4.367</v>
-      </c>
-      <c r="AH4">
-        <v>0.005531195368698593</v>
-      </c>
-      <c r="AI4">
-        <v>0.04495690659212673</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1439686150397257</v>
-      </c>
-      <c r="AK4">
-        <v>16.35580524344567</v>
-      </c>
-      <c r="AL4">
-        <v>0.001</v>
-      </c>
-      <c r="AM4">
-        <v>0.001</v>
-      </c>
-      <c r="AO4">
-        <v>-1380</v>
-      </c>
-      <c r="AQ4">
-        <v>-1380</v>
+        <v>-6.240768094534712</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_precious_metals.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.118</v>
+        <v>-0.287</v>
       </c>
       <c r="G2">
-        <v>-0.2711267605633803</v>
+        <v>-1.498855835240275</v>
       </c>
       <c r="H2">
-        <v>-0.2711267605633803</v>
+        <v>-1.498855835240275</v>
       </c>
       <c r="I2">
-        <v>-1.190140845070423</v>
+        <v>-1.659038901601831</v>
       </c>
       <c r="J2">
-        <v>-1.190140845070423</v>
+        <v>-1.659038901601831</v>
       </c>
       <c r="K2">
-        <v>-12.1</v>
+        <v>-6.51</v>
       </c>
       <c r="L2">
-        <v>-0.852112676056338</v>
+        <v>-0.7448512585812357</v>
       </c>
       <c r="M2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.003868471953578337</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.001652892561983471</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.02</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.442</v>
+        <v>0.358</v>
       </c>
       <c r="V2">
-        <v>0.08549323017408124</v>
+        <v>0.04031531531531531</v>
       </c>
       <c r="W2">
-        <v>-0.4708171206225681</v>
+        <v>-0.5380165289256198</v>
       </c>
       <c r="X2">
-        <v>1.418785559773485</v>
+        <v>0.8656324392553461</v>
       </c>
       <c r="Y2">
-        <v>-1.889602680396053</v>
+        <v>-1.403648968180966</v>
       </c>
       <c r="Z2">
-        <v>0.3438423168192164</v>
+        <v>0.2359101705895055</v>
       </c>
       <c r="AA2">
-        <v>-0.4092207855101941</v>
+        <v>-0.3913841502915137</v>
       </c>
       <c r="AB2">
-        <v>0.3787528471016532</v>
+        <v>0.2686721489407864</v>
       </c>
       <c r="AC2">
-        <v>-0.7879736326118474</v>
+        <v>-0.6600562992323</v>
       </c>
       <c r="AD2">
-        <v>29.4</v>
+        <v>35.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>29.4</v>
+        <v>35.6</v>
       </c>
       <c r="AG2">
-        <v>28.958</v>
+        <v>35.242</v>
       </c>
       <c r="AH2">
-        <v>0.8504483656349435</v>
+        <v>0.8003597122302157</v>
       </c>
       <c r="AI2">
-        <v>0.7368421052631579</v>
+        <v>0.8702028843803471</v>
       </c>
       <c r="AJ2">
-        <v>0.8485114861697139</v>
+        <v>0.7987398576673768</v>
       </c>
       <c r="AK2">
-        <v>0.733894267322216</v>
+        <v>0.8690570132175971</v>
       </c>
       <c r="AL2">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AM2">
-        <v>2.708</v>
+        <v>2.739</v>
       </c>
       <c r="AN2">
-        <v>-2.556521739130435</v>
+        <v>-2.803149606299213</v>
       </c>
       <c r="AO2">
-        <v>-5.827586206896552</v>
+        <v>-4.849498327759197</v>
       </c>
       <c r="AP2">
-        <v>-2.518086956521739</v>
+        <v>-2.77496062992126</v>
       </c>
       <c r="AQ2">
-        <v>-6.240768094534712</v>
+        <v>-5.293902884264329</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.118</v>
+        <v>-0.287</v>
       </c>
       <c r="G3">
-        <v>-0.2711267605633803</v>
+        <v>-1.498855835240275</v>
       </c>
       <c r="H3">
-        <v>-0.2711267605633803</v>
+        <v>-1.498855835240275</v>
       </c>
       <c r="I3">
-        <v>-1.190140845070423</v>
+        <v>-1.659038901601831</v>
       </c>
       <c r="J3">
-        <v>-1.190140845070423</v>
+        <v>-1.659038901601831</v>
       </c>
       <c r="K3">
-        <v>-12.1</v>
+        <v>-6.51</v>
       </c>
       <c r="L3">
-        <v>-0.852112676056338</v>
+        <v>-0.7448512585812357</v>
       </c>
       <c r="M3">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.003868471953578337</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.001652892561983471</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.02</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.442</v>
+        <v>0.358</v>
       </c>
       <c r="V3">
-        <v>0.08549323017408124</v>
+        <v>0.04031531531531531</v>
       </c>
       <c r="W3">
-        <v>-0.4708171206225681</v>
+        <v>-0.5380165289256198</v>
       </c>
       <c r="X3">
-        <v>1.418785559773485</v>
+        <v>0.8656324392553461</v>
       </c>
       <c r="Y3">
-        <v>-1.889602680396053</v>
+        <v>-1.403648968180966</v>
       </c>
       <c r="Z3">
-        <v>0.3438423168192164</v>
+        <v>0.2359101705895055</v>
       </c>
       <c r="AA3">
-        <v>-0.4092207855101941</v>
+        <v>-0.3913841502915137</v>
       </c>
       <c r="AB3">
-        <v>0.3787528471016532</v>
+        <v>0.2686721489407864</v>
       </c>
       <c r="AC3">
-        <v>-0.7879736326118474</v>
+        <v>-0.6600562992323</v>
       </c>
       <c r="AD3">
-        <v>29.4</v>
+        <v>35.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>29.4</v>
+        <v>35.6</v>
       </c>
       <c r="AG3">
-        <v>28.958</v>
+        <v>35.242</v>
       </c>
       <c r="AH3">
-        <v>0.8504483656349435</v>
+        <v>0.8003597122302157</v>
       </c>
       <c r="AI3">
-        <v>0.7368421052631579</v>
+        <v>0.8702028843803471</v>
       </c>
       <c r="AJ3">
-        <v>0.8485114861697139</v>
+        <v>0.7987398576673768</v>
       </c>
       <c r="AK3">
-        <v>0.733894267322216</v>
+        <v>0.8690570132175971</v>
       </c>
       <c r="AL3">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AM3">
-        <v>2.708</v>
+        <v>2.739</v>
       </c>
       <c r="AN3">
-        <v>-2.556521739130435</v>
+        <v>-2.803149606299213</v>
       </c>
       <c r="AO3">
-        <v>-5.827586206896552</v>
+        <v>-4.849498327759197</v>
       </c>
       <c r="AP3">
-        <v>-2.518086956521739</v>
+        <v>-2.77496062992126</v>
       </c>
       <c r="AQ3">
-        <v>-6.240768094534712</v>
+        <v>-5.293902884264329</v>
       </c>
     </row>
   </sheetData>
